--- a/measurements/34/Filled_2D_sections/axial/week34_axial_Batch_Allmarks.xlsx
+++ b/measurements/34/Filled_2D_sections/axial/week34_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,107 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +601,79 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11.46698393813207</v>
+        <v>4370.975056689342</v>
       </c>
       <c r="D2" t="n">
-        <v>29.3922532215351</v>
+        <v>573.8487533728281</v>
       </c>
       <c r="E2" t="n">
-        <v>15.09473994592341</v>
+        <v>294.7068275156475</v>
       </c>
       <c r="F2" t="n">
         <v>1.947185133816961</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1667989479729818</v>
+        <v>0.1667989479729817</v>
       </c>
       <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.577380952380952</v>
+      </c>
+      <c r="J2" t="n">
+        <v>38.00223214285714</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.124599358974358</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>38.00223214285714</v>
+      </c>
+      <c r="N2" t="n">
+        <v>18.38541666666666</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.62797619047619</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.80691964285714</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.359162414965986</v>
+      </c>
+      <c r="Z2" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.5949885670731707</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.946455792682927</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.034775152439024</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="AA2" t="n">
+        <v>1.577380952380952</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.900669642857143</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.679501488095238</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>11.6911511005354</v>
+      <c r="AH2" s="2" t="n">
+        <v>4456.422902494331</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +684,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.68441403926234</v>
+        <v>4453.854875283447</v>
       </c>
       <c r="D3" t="n">
-        <v>27.36266289396984</v>
+        <v>534.2234184060777</v>
       </c>
       <c r="E3" t="n">
-        <v>15.06963169574738</v>
+        <v>294.2166188217345</v>
       </c>
       <c r="F3" t="n">
         <v>1.815748615919494</v>
@@ -572,24 +703,60 @@
         <v>0.1961101545267031</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5930830792682927</v>
+        <v>1.806175595238095</v>
       </c>
       <c r="J3" t="n">
-        <v>1.878144054878049</v>
+        <v>36.66852678571428</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9935689786585367</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>8.039301658163264</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>36.66852678571428</v>
+      </c>
+      <c r="N3" t="n">
+        <v>17.24702380952381</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4.825148809523809</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.09821428571428</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.73735119047619</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.806175595238095</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4.192708333333333</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.84970238095238</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>22.93786718336548</v>
+      <c r="AH3" s="2" t="n">
+        <v>447.8345497704688</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +767,79 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11.73735871505056</v>
+        <v>4474.036281179138</v>
       </c>
       <c r="D4" t="n">
-        <v>26.89996626318955</v>
+        <v>525.189817519415</v>
       </c>
       <c r="E4" t="n">
-        <v>15.18984957148389</v>
+        <v>296.5637297289712</v>
       </c>
       <c r="F4" t="n">
         <v>1.77091722578275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2038340675416866</v>
+        <v>0.2038340675416867</v>
       </c>
       <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.590401785714286</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.87983630952381</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.081473214285714</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>35.87983630952381</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17.26376488095238</v>
+      </c>
+      <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.5863185975609756</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.837747713414634</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.9831126143292683</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="W4" t="n">
+        <v>4.376860119047619</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12.18563988095238</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.257533482142858</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.590401785714286</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.131324404761904</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.71298363095238</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>14.52304001843057</v>
+      <c r="AH4" s="2" t="n">
+        <v>283.5450670265016</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +850,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.95776323616895</v>
+        <v>4558.049886621315</v>
       </c>
       <c r="D5" t="n">
-        <v>26.53381522108869</v>
+        <v>518.0411543164934</v>
       </c>
       <c r="E5" t="n">
-        <v>14.79022092354007</v>
+        <v>288.7614561262585</v>
       </c>
       <c r="F5" t="n">
         <v>1.794010742520928</v>
@@ -666,23 +869,62 @@
         <v>0.2134324321145454</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5300114329268293</v>
+        <v>1.506696428571428</v>
       </c>
       <c r="J5" t="n">
-        <v>1.811642530487805</v>
+        <v>35.37016369047619</v>
       </c>
       <c r="K5" t="n">
-        <v>0.897141768292683</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>7.743303571428569</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>35.37016369047619</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16.88244047619047</v>
+      </c>
+      <c r="O5" t="n">
+        <v>13.27938988095238</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11.69828869047619</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10.34784226190476</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.801711309523809</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.506696428571428</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.092261904761904</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.529968584656084</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AH5" s="2" t="n">
         <v>1.57589876765548</v>
       </c>
     </row>
@@ -694,17 +936,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.96490184414039</v>
+        <v>4560.770975056689</v>
       </c>
       <c r="D6" t="n">
-        <v>26.82649815373304</v>
+        <v>523.7554401443118</v>
       </c>
       <c r="E6" t="n">
-        <v>14.74980980593984</v>
+        <v>287.9724771635873</v>
       </c>
       <c r="F6" t="n">
         <v>1.818769089682082</v>
@@ -713,23 +955,62 @@
         <v>0.2089252999272678</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5648818597560976</v>
+        <v>1.58110119047619</v>
       </c>
       <c r="J6" t="n">
-        <v>1.796208079268293</v>
+        <v>35.06882440476191</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9357088414634148</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>9.58984375</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>35.06882440476191</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16.85825892857143</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11.72061011904762</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11.02864583333333</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.690848214285714</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.58110119047619</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.066220238095238</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.840711805555555</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AH6" s="2" t="n">
         <v>0.2907241323653617</v>
       </c>
     </row>
@@ -741,17 +1022,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.08447352766211</v>
+        <v>4606.349206349206</v>
       </c>
       <c r="D7" t="n">
-        <v>23.92131039282171</v>
+        <v>467.0351076693761</v>
       </c>
       <c r="E7" t="n">
-        <v>14.79613894660299</v>
+        <v>288.8769984812964</v>
       </c>
       <c r="F7" t="n">
         <v>1.61672653110045</v>
@@ -760,24 +1041,57 @@
         <v>0.2653796799924891</v>
       </c>
       <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.592261904761905</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.52418154761905</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.449745783730156</v>
+      </c>
+      <c r="L7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.709984756097561</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.409775152439025</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.9673208841463415</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>13.86160714285714</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>27.52418154761905</v>
+      </c>
+      <c r="R7" t="n">
+        <v>18.88578869047619</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4.92001488095238</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.592261904761905</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.90625</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.990539965986394</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>3.25</v>
+      <c r="AH7" s="2" t="n">
+        <v>14.65</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1102,76 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.0609756097561</v>
+        <v>4597.392290249432</v>
       </c>
       <c r="D8" t="n">
-        <v>24.00458389666023</v>
+        <v>468.6609236966996</v>
       </c>
       <c r="E8" t="n">
-        <v>14.80205699001871</v>
+        <v>288.9925412336985</v>
       </c>
       <c r="F8" t="n">
         <v>1.621705950250492</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2630291847626187</v>
+        <v>0.2630291847626186</v>
       </c>
       <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.618303571428571</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.73177083333333</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.343563988095237</v>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.7105564024390244</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.369188262195122</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.9573170731707317</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>13.87276785714286</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>26.73177083333333</v>
+      </c>
+      <c r="R8" t="n">
+        <v>18.69047619047619</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.890997023809524</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.618303571428571</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.617931547619047</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.78140943877551</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.7288443216463415</v>
+      <c r="AH8" s="2" t="n">
+        <v>1.544921875</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1182,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.13593099345628</v>
+        <v>4625.963718820862</v>
       </c>
       <c r="D9" t="n">
-        <v>21.6645564567752</v>
+        <v>422.9746736798967</v>
       </c>
       <c r="E9" t="n">
-        <v>14.81042640674405</v>
+        <v>289.1559441316695</v>
       </c>
       <c r="F9" t="n">
         <v>1.462790865150923</v>
@@ -854,24 +1201,57 @@
         <v>0.3249251725506894</v>
       </c>
       <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.811755952380952</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.63058035714285</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.516910173160174</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.7429496951219512</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.312785823170732</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9447408536585366</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>25.63058035714285</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15.19903273809524</v>
+      </c>
+      <c r="O9" t="n">
+        <v>14.50520833333333</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.356770833333333</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.811755952380952</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.543526785714286</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.856345663265306</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.45269150152439</v>
+      <c r="AH9" s="2" t="n">
+        <v>28.36207217261905</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1262,76 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12.07495538370018</v>
+        <v>4602.721088435374</v>
       </c>
       <c r="D10" t="n">
-        <v>21.69068005608349</v>
+        <v>423.4847058568682</v>
       </c>
       <c r="E10" t="n">
-        <v>14.94594709756898</v>
+        <v>291.8018242858705</v>
       </c>
       <c r="F10" t="n">
         <v>1.451275045635052</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3225143640648087</v>
+        <v>0.3225143640648086</v>
       </c>
       <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.98139880952381</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.364468864468865</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.7429496951219512</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.27953506097561</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.9226054369918698</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>24.98139880952381</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14.55171130952381</v>
+      </c>
+      <c r="O10" t="n">
+        <v>14.50520833333333</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.875</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.27046130952381</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.484002976190476</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.424975198412698</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.000407774390244</v>
+      <c r="AH10" s="2" t="n">
+        <v>6.873711097201118</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1342,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11.88221296847115</v>
+        <v>4529.251700680272</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31992372070871</v>
+        <v>435.7699393090747</v>
       </c>
       <c r="E11" t="n">
-        <v>14.89716665919234</v>
+        <v>290.8494442985171</v>
       </c>
       <c r="F11" t="n">
         <v>1.49826636375422</v>
@@ -948,16 +1361,57 @@
         <v>0.2997241822912439</v>
       </c>
       <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.38578869047619</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24.53125</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.203629889455781</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.721703506097561</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.256478658536585</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.9842479674796749</v>
+      <c r="M11" t="n">
+        <v>24.53125</v>
+      </c>
+      <c r="N11" t="n">
+        <v>19.02715773809524</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14.09040178571428</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.143229166666666</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.38578869047619</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.835565476190476</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.405877976190476</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>2.65</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1422,76 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.84919690660321</v>
+        <v>4516.666666666666</v>
       </c>
       <c r="D12" t="n">
-        <v>22.73975792163756</v>
+        <v>443.9667022795904</v>
       </c>
       <c r="E12" t="n">
-        <v>14.74490713200918</v>
+        <v>287.8767582916078</v>
       </c>
       <c r="F12" t="n">
         <v>1.542210996519106</v>
       </c>
       <c r="G12" t="n">
-        <v>0.287956646000163</v>
+        <v>0.2879566460001631</v>
       </c>
       <c r="H12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="J12" t="n">
+        <v>24.52380952380952</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.378082482993197</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.7696265243902439</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.25609756097561</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.9932672764227641</v>
+      <c r="M12" t="n">
+        <v>24.52380952380952</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18.62723214285714</v>
+      </c>
+      <c r="O12" t="n">
+        <v>15.02604166666667</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.086309523809524</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.757440476190476</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.502976190476191</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>28.4991939484127</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1502,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.71980963712076</v>
+        <v>4467.346938775509</v>
       </c>
       <c r="D13" t="n">
-        <v>21.85376034713373</v>
+        <v>426.6686543964204</v>
       </c>
       <c r="E13" t="n">
-        <v>14.64142808972336</v>
+        <v>285.8564531803131</v>
       </c>
       <c r="F13" t="n">
         <v>1.492597594525129</v>
@@ -1026,16 +1521,63 @@
         <v>0.3083742236822136</v>
       </c>
       <c r="H13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.497395833333333</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24.10714285714285</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.422758556547618</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.8609946646341464</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.234756097560976</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.9915205792682927</v>
+      <c r="M13" t="n">
+        <v>24.10714285714285</v>
+      </c>
+      <c r="N13" t="n">
+        <v>17.15773809523809</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16.80989583333333</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8.2421875</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6.573660714285714</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.443824404761904</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.497395833333333</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.967633928571428</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.54296875</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>17.16135499338624</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1588,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.68828078524688</v>
+        <v>4455.32879818594</v>
       </c>
       <c r="D14" t="n">
-        <v>22.06071845496573</v>
+        <v>430.7092650731404</v>
       </c>
       <c r="E14" t="n">
-        <v>14.52957963071218</v>
+        <v>283.6727451710474</v>
       </c>
       <c r="F14" t="n">
         <v>1.518331501369417</v>
@@ -1065,16 +1607,63 @@
         <v>0.3018013623653772</v>
       </c>
       <c r="H14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.04278273809524</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.126612103174605</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.7797256097560976</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.282679115853659</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.9755779979674797</v>
+      <c r="M14" t="n">
+        <v>25.04278273809524</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16.875</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15.22321428571428</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4.389880952380953</v>
+      </c>
+      <c r="X14" t="n">
+        <v>9.213169642857142</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.456473214285714</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.578869047619047</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.482920725108225</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>15.04877645502645</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1674,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.69303985722784</v>
+        <v>4457.142857142857</v>
       </c>
       <c r="D15" t="n">
-        <v>21.75619938896924</v>
+        <v>424.7638928322565</v>
       </c>
       <c r="E15" t="n">
-        <v>14.42610058261127</v>
+        <v>281.65243994622</v>
       </c>
       <c r="F15" t="n">
         <v>1.508113662758834</v>
@@ -1104,16 +1693,63 @@
         <v>0.3104353956374328</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5387766768292683</v>
+        <v>1.683407738095238</v>
       </c>
       <c r="J15" t="n">
-        <v>1.289634146341464</v>
+        <v>25.17857142857143</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8567311356707319</v>
+        <v>6.398925781250001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25.17857142857143</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15.87611607142857</v>
+      </c>
+      <c r="O15" t="n">
+        <v>15.33296130952381</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10.51897321428571</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5.42782738095238</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.76376488095238</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.683407738095238</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.199404761904762</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.528459821428571</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>13.8671875</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1760,79 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11.68411659726353</v>
+        <v>4453.741496598639</v>
       </c>
       <c r="D16" t="n">
-        <v>20.56669812958415</v>
+        <v>401.5402968156905</v>
       </c>
       <c r="E16" t="n">
-        <v>14.2762923996623</v>
+        <v>278.7276135172162</v>
       </c>
       <c r="F16" t="n">
         <v>1.440619003437521</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3471175715829379</v>
+        <v>0.347117571582938</v>
       </c>
       <c r="H16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.901041666666667</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25.38876488095238</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.884021577380953</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>25.38876488095238</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15.79613095238095</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.5637385670731707</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.300400152439025</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.8910696138211381</v>
+      <c r="T16" t="n">
+        <v>11.0063244047619</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6.393229166666666</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.547991071428571</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.901041666666667</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.989955357142857</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.819264069264069</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>27.12797619047619</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1843,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11.51397977394408</v>
+        <v>4388.888888888889</v>
       </c>
       <c r="D17" t="n">
-        <v>20.1729874814429</v>
+        <v>393.8535651138851</v>
       </c>
       <c r="E17" t="n">
-        <v>13.99197888955837</v>
+        <v>273.1767307009015</v>
       </c>
       <c r="F17" t="n">
         <v>1.441753710513182</v>
@@ -1182,16 +1862,60 @@
         <v>0.3555452559425825</v>
       </c>
       <c r="H17" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.655505952380952</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26.10119047619047</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.898088727678572</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.834984756097561</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.336890243902439</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.0859375</v>
+      <c r="M17" t="n">
+        <v>26.10119047619047</v>
+      </c>
+      <c r="N17" t="n">
+        <v>16.30208333333333</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.428943452380953</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8.870907738095237</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.743117559523809</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.655505952380952</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.075520833333333</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.899367559523809</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>18.78813244047619</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1926,79 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.43932183224271</v>
+        <v>4360.430839002267</v>
       </c>
       <c r="D18" t="n">
-        <v>19.92316701935559</v>
+        <v>388.9761179969424</v>
       </c>
       <c r="E18" t="n">
-        <v>13.95503452056792</v>
+        <v>272.4554358777546</v>
       </c>
       <c r="F18" t="n">
         <v>1.42766877358787</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3621540873336506</v>
+        <v>0.3621540873336505</v>
       </c>
       <c r="H18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.512276785714286</v>
+      </c>
+      <c r="J18" t="n">
+        <v>26.37276785714285</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.692661830357143</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.825171493902439</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.350800304878049</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.087985899390244</v>
+      <c r="M18" t="n">
+        <v>26.37276785714285</v>
+      </c>
+      <c r="N18" t="n">
+        <v>16.11049107142857</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.47172619047619</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.729166666666666</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4.987444196428571</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.512276785714286</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.932291666666667</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.864955357142857</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +2009,76 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.2180249851279</v>
+        <v>4276.077097505668</v>
       </c>
       <c r="D19" t="n">
-        <v>19.57823689100219</v>
+        <v>382.2417678719475</v>
       </c>
       <c r="E19" t="n">
-        <v>13.74807645634907</v>
+        <v>268.4148260525295</v>
       </c>
       <c r="F19" t="n">
         <v>1.424070992997763</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3677723788357478</v>
+        <v>0.3677723788357479</v>
       </c>
       <c r="H19" t="n">
+        <v>17</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.672247023809524</v>
+      </c>
+      <c r="J19" t="n">
+        <v>26.10491071428571</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.164565826330533</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.9377858231707318</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.337080792682927</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.137433307926829</v>
+      <c r="M19" t="n">
+        <v>26.10491071428571</v>
+      </c>
+      <c r="N19" t="n">
+        <v>18.30915178571428</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.164806547619047</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.125744047619047</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.672247023809524</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.861607142857143</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.699461996336997</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>7.539726828231292</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2089,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.07168352171327</v>
+        <v>4220.294784580498</v>
       </c>
       <c r="D20" t="n">
-        <v>19.46883976750258</v>
+        <v>380.1059192702884</v>
       </c>
       <c r="E20" t="n">
-        <v>13.55540587843918</v>
+        <v>264.6531623885745</v>
       </c>
       <c r="F20" t="n">
         <v>1.436241743116606</v>
@@ -1299,16 +2108,54 @@
         <v>0.3670653461473273</v>
       </c>
       <c r="H20" t="n">
+        <v>16</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.335565476190476</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25.99144345238095</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.328078497023809</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.9779916158536586</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.331269054878049</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.154630335365854</v>
+      <c r="M20" t="n">
+        <v>25.99144345238095</v>
+      </c>
+      <c r="N20" t="n">
+        <v>19.09412202380952</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.462425595238095</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.335565476190476</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.692336309523809</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.746251144688645</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>6.978369472789114</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2166,79 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.89559785841761</v>
+        <v>4153.174603174602</v>
       </c>
       <c r="D21" t="n">
-        <v>20.02072798915026</v>
+        <v>390.8808797881717</v>
       </c>
       <c r="E21" t="n">
-        <v>13.44600874621694</v>
+        <v>262.5173136166164</v>
       </c>
       <c r="F21" t="n">
-        <v>1.488971810670815</v>
+        <v>1.488971810670816</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3415868940347675</v>
+        <v>0.3415868940347673</v>
       </c>
       <c r="H21" t="n">
+        <v>16</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.372767857142857</v>
+      </c>
+      <c r="J21" t="n">
+        <v>28.04129464285714</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.723586309523811</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.9906631097560976</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.436261432926829</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.213462271341463</v>
+      <c r="M21" t="n">
+        <v>28.04129464285714</v>
+      </c>
+      <c r="N21" t="n">
+        <v>19.34151785714286</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7.470238095238095</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.951636904761904</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.372767857142857</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.843005952380952</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.498816287878788</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>5.088975694444444</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2248,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>4.520089285714286</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2270,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>10.15066964285714</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2287,90 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>6.756847009637188</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>1.544921875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>3.833426339285714</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>2.682872901734509</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/34/Filled_2D_sections/axial/week34_axial_Batch_Allmarks.xlsx
+++ b/measurements/34/Filled_2D_sections/axial/week34_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2376,4 +2582,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week34_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4456.422902494331</v>
+      </c>
+      <c r="D10" t="n">
+        <v>130.6682761530413</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4153.174603174602</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4625.963718820862</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>447.8345497704688</v>
+      </c>
+      <c r="D11" t="n">
+        <v>58.09316084349666</v>
+      </c>
+      <c r="E11" t="n">
+        <v>380.1059192702884</v>
+      </c>
+      <c r="F11" t="n">
+        <v>573.8487533728281</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.57589876765548</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1626186146816324</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.424070992997763</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.947185133816961</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2907241323653617</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.06318767849294779</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1667989479729817</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3677723788357479</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>13</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0165.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>18</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0169.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0171.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>16</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>16</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>17</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>13</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>17</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>13</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>13</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>16</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>16</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>11</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.954078056944394</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6708203932499369</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.650358812660543</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>53</v>
+      </c>
+      <c r="C48" t="n">
+        <v>20.89875336927224</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.660132349684732</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.27938988095238</v>
+      </c>
+      <c r="F48" t="n">
+        <v>38.00223214285714</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>55</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.853050595238094</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.450419267477657</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.125744047619047</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12.80691964285714</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>185</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.669642857142857</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5695554971153143</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.192708333333333</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>